--- a/data/assumptions.xlsx
+++ b/data/assumptions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aheller\Documents\GitHub\TEA.CART\inst\app\www\static_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/slarue_camsys_com/Documents/Documents/idot_github_puller/TEACART/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4DE7A5-301F-484D-A9F6-6366FD901580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{8B4DE7A5-301F-484D-A9F6-6366FD901580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3DE427-73F4-4A31-90F1-E381957C9E57}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{DDC5952C-C9D2-418E-96AF-132B646A875F}"/>
+    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="8" xr2:uid="{DDC5952C-C9D2-418E-96AF-132B646A875F}"/>
   </bookViews>
   <sheets>
     <sheet name="bikeped" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="mhdv" sheetId="6" r:id="rId6"/>
     <sheet name="pnr" sheetId="7" r:id="rId7"/>
     <sheet name="evsi" sheetId="8" r:id="rId8"/>
+    <sheet name="landuse" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="105">
   <si>
     <t>Bicycle and Pedestrian Data</t>
   </si>
@@ -304,13 +305,70 @@
   </si>
   <si>
     <t>Element</t>
+  </si>
+  <si>
+    <t>Land Use (Smart Growth) Incentives</t>
+  </si>
+  <si>
+    <t>$ Per Household Shifted</t>
+  </si>
+  <si>
+    <t>Elasticity of VMT w/r/t residential density</t>
+  </si>
+  <si>
+    <t>Elasticity of VMT w/r/t job density</t>
+  </si>
+  <si>
+    <t>VMT per Household</t>
+  </si>
+  <si>
+    <t>Work VMT per Employee</t>
+  </si>
+  <si>
+    <t>Work Trip Length</t>
+  </si>
+  <si>
+    <t>Work Annualization</t>
+  </si>
+  <si>
+    <t>VMT Per Capita</t>
+  </si>
+  <si>
+    <t>Suburban (High VMT)</t>
+  </si>
+  <si>
+    <t>Urban (Low VMT)</t>
+  </si>
+  <si>
+    <t>Elasticity of VMT</t>
+  </si>
+  <si>
+    <t>Land Use Incentive</t>
+  </si>
+  <si>
+    <t>Commute Factors</t>
+  </si>
+  <si>
+    <t>Household Factors</t>
+  </si>
+  <si>
+    <t>People per Household</t>
+  </si>
+  <si>
+    <t>Square feet of building space per employee</t>
+  </si>
+  <si>
+    <t>Employees per acre at 1.0 FAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,13 +376,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -339,8 +423,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -359,9 +451,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -399,7 +491,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -505,7 +597,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -647,7 +739,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -656,18 +748,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{966E85B1-EFA7-4717-AF13-52589B25DBA3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -678,7 +770,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -689,7 +781,7 @@
         <v>0.47249999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -700,7 +792,7 @@
         <v>0.59249999999999992</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -711,7 +803,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -722,7 +814,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -733,7 +825,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -744,7 +836,7 @@
         <v>2.2999999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -763,19 +855,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DA4A77F-DF97-4D8A-86F5-EF2FA03A42A8}">
   <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -786,7 +878,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -797,7 +889,7 @@
         <v>4.9280000000000008</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -808,7 +900,7 @@
         <v>4.4352000000000009</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -819,7 +911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -830,7 +922,7 @@
         <v>7.8398072040762292</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -841,7 +933,7 @@
         <v>7.0558264836686062</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -852,7 +944,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -863,7 +955,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -874,7 +966,7 @@
         <v>6.75</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -885,7 +977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -896,7 +988,7 @@
         <v>4.1328553316289787</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -907,7 +999,7 @@
         <v>4.1328553316289787</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -918,7 +1010,7 @@
         <v>9.937972153462713</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -929,7 +1021,7 @@
         <v>9.937972153462713</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -940,7 +1032,7 @@
         <v>28.751266631655319</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -951,7 +1043,7 @@
         <v>5.7158402899079999</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -962,7 +1054,7 @@
         <v>4.5815735448855488</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -973,7 +1065,7 @@
         <v>29.528319416465337</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -984,7 +1076,7 @@
         <v>8.7064741214944306</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -995,7 +1087,7 @@
         <v>5.9971295125527684</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1006,7 +1098,7 @@
         <v>1.1264220020975759</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1017,7 +1109,7 @@
         <v>1.6007310428935415</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1028,7 +1120,7 @@
         <v>15.699592556616064</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>30</v>
       </c>
@@ -1039,7 +1131,7 @@
         <v>13.186207999692673</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1050,7 +1142,7 @@
         <v>7.4129098007451137</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -1061,7 +1153,7 @@
         <v>40.797256605599621</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -1072,7 +1164,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1083,7 +1175,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -1094,7 +1186,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -1105,7 +1197,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1116,7 +1208,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>31</v>
       </c>
@@ -1127,7 +1219,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -1138,7 +1230,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -1149,7 +1241,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -1160,7 +1252,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -1171,7 +1263,7 @@
         <v>39214.140781108086</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -1182,7 +1274,7 @@
         <v>20740.464285714286</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -1193,7 +1285,7 @@
         <v>37760.397350993378</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>33</v>
       </c>
@@ -1204,7 +1296,7 @@
         <v>14393.643564356436</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>33</v>
       </c>
@@ -1215,7 +1307,7 @@
         <v>23700.05</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>33</v>
       </c>
@@ -1226,7 +1318,7 @@
         <v>79462.921052631573</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>33</v>
       </c>
@@ -1237,7 +1329,7 @@
         <v>81116.092592592599</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -1248,7 +1340,7 @@
         <v>44645.617449664431</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -1259,7 +1351,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>34</v>
       </c>
@@ -1270,7 +1362,7 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -1281,7 +1373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>34</v>
       </c>
@@ -1292,7 +1384,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>34</v>
       </c>
@@ -1303,7 +1395,7 @@
         <v>0.54545454545454541</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>34</v>
       </c>
@@ -1322,18 +1414,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F08883B-38C6-4A43-8522-0486E83E335F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1344,7 +1436,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -1355,7 +1447,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>42</v>
       </c>
@@ -1366,7 +1458,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1385,18 +1477,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{558E0145-DBD0-4D9B-BF29-D7FFBFF9A807}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1407,7 +1499,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -1418,7 +1510,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -1429,7 +1521,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -1440,7 +1532,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -1451,7 +1543,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -1470,19 +1562,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B13BC45-10C4-4074-8516-C52F324AD237}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1493,7 +1585,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>54</v>
       </c>
@@ -1504,7 +1596,7 @@
         <v>28835.152377985909</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -1515,7 +1607,7 @@
         <v>17447.589560403594</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -1526,7 +1618,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>57</v>
       </c>
@@ -1537,7 +1629,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1548,7 +1640,7 @@
         <v>20213.868050974328</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -1559,7 +1651,7 @@
         <v>8617.6405996773447</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -1570,7 +1662,7 @@
         <v>5454.1490292354583</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1581,7 +1673,7 @@
         <v>2265.3440244453095</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -1592,7 +1684,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1603,7 +1695,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -1614,7 +1706,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -1625,7 +1717,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>64</v>
       </c>
@@ -1636,7 +1728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -1647,7 +1739,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -1658,7 +1750,7 @@
         <v>-0.3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1677,18 +1769,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12442B84-87BF-4DCD-AE1B-18D8EC41A89D}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1699,7 +1791,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1710,7 +1802,7 @@
         <v>10332.716678401948</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -1721,7 +1813,7 @@
         <v>15008.384525421716</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>70</v>
       </c>
@@ -1732,7 +1824,7 @@
         <v>33694.611571910202</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>70</v>
       </c>
@@ -1751,14 +1843,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D7A8CF6-AD23-4E6D-A194-851246FF52E1}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -1766,7 +1858,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>76</v>
       </c>
@@ -1782,19 +1874,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E7019AF-A15D-42D3-9A55-633A092225C6}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -1805,7 +1897,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -1816,7 +1908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>78</v>
       </c>
@@ -1827,7 +1919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>78</v>
       </c>
@@ -1838,7 +1930,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>78</v>
       </c>
@@ -1849,7 +1941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>78</v>
       </c>
@@ -1858,6 +1950,170 @@
       </c>
       <c r="C7">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A72AB935-AD54-4D2F-BC8B-2931EEF1F8AF}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="4">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="4">
+        <v>10553</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="4">
+        <v>7646</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="5">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="4">
+        <v>19642</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="4">
+        <v>6350</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="6">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="4">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="4">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="4">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/data/assumptions.xlsx
+++ b/data/assumptions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://camsys-my.sharepoint.com/personal/slarue_camsys_com/Documents/Documents/idot_github_puller/TEACART/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{8B4DE7A5-301F-484D-A9F6-6366FD901580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C3DE427-73F4-4A31-90F1-E381957C9E57}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{8B4DE7A5-301F-484D-A9F6-6366FD901580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E13AD0C2-3C27-4113-A1DE-B7A6752852FF}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="8" xr2:uid="{DDC5952C-C9D2-418E-96AF-132B646A875F}"/>
+    <workbookView xWindow="270" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{DDC5952C-C9D2-418E-96AF-132B646A875F}"/>
   </bookViews>
   <sheets>
     <sheet name="bikeped" sheetId="1" r:id="rId1"/>
@@ -253,9 +253,6 @@
     <t>VMT w/r/t travel time (rural)</t>
   </si>
   <si>
-    <t>Medium and Heavy Duty Vehicle Replacement</t>
-  </si>
-  <si>
     <t>Miles per Vehicle per Year</t>
   </si>
   <si>
@@ -359,6 +356,9 @@
   </si>
   <si>
     <t>Employees per acre at 1.0 FAR</t>
+  </si>
+  <si>
+    <t>Medium- and Heavy-Duty Vehicle Replacement</t>
   </si>
 </sst>
 </file>
@@ -761,13 +761,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -869,13 +869,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1427,13 +1427,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1490,13 +1490,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1576,13 +1576,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1777,26 +1777,26 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
         <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>71</v>
       </c>
       <c r="C3">
         <v>10332.716678401948</v>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4">
         <v>15008.384525421716</v>
@@ -1815,10 +1815,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5">
         <v>33694.611571910202</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6">
         <v>12000</v>
@@ -1847,20 +1847,20 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3">
         <v>0.25</v>
@@ -1883,26 +1883,26 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" t="s">
         <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>79</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1910,10 +1910,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1932,10 +1932,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -1969,27 +1969,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="4">
         <v>25000</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="C4" s="4">
         <v>10553</v>
@@ -2008,10 +2008,10 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C5" s="4">
         <v>7646</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="5">
         <v>-0.22</v>
@@ -2030,10 +2030,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C7" s="5">
         <v>-7.0000000000000007E-2</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4">
         <v>19642</v>
@@ -2052,10 +2052,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="C9" s="4">
         <v>2.5</v>
@@ -2063,10 +2063,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C10" s="4">
         <v>6350</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" s="6">
         <v>12.7</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C12" s="4">
         <v>250</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="4">
         <v>300</v>
@@ -2107,10 +2107,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="4">
         <v>145</v>
